--- a/src/annotation_template.xlsx
+++ b/src/annotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18154F44-DA5E-4399-B3CF-B877FE15295F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E989B231-D952-4251-88F4-C1AE8E53DCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="51">
   <si>
     <t>Work</t>
   </si>
@@ -180,9 +180,6 @@
     <t>Classe</t>
   </si>
   <si>
-    <t>E55 Types</t>
-  </si>
-  <si>
     <t>rdf: relation</t>
   </si>
   <si>
@@ -190,6 +187,9 @@
   </si>
   <si>
     <t>sequences G5 Narrative Event</t>
+  </si>
+  <si>
+    <t>novum introduced by</t>
   </si>
 </sst>
 </file>
@@ -345,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -403,6 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -702,13 +703,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -764,15 +765,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -785,16 +786,16 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -840,20 +841,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
     </row>
     <row r="2" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -931,28 +932,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{986016D8-19A6-42C1-B729-6B723408289C}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.44140625" customWidth="1"/>
     <col min="2" max="2" width="26.88671875" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="5" max="5" width="27.77734375" customWidth="1"/>
-    <col min="6" max="6" width="25.21875" customWidth="1"/>
+    <col min="5" max="5" width="26.6640625" style="22" customWidth="1"/>
+    <col min="6" max="6" width="27.77734375" customWidth="1"/>
+    <col min="7" max="7" width="25.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -966,31 +969,36 @@
         <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1010,15 +1018,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1082,14 +1090,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1150,16 +1158,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1228,14 +1236,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1335,17 +1343,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1456,12 +1464,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
